--- a/output/pdf_financials_xlsx/TELI.xlsx
+++ b/output/pdf_financials_xlsx/TELI.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/TELI.xlsx
+++ b/output/pdf_financials_xlsx/TELI.xlsx
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>1.452539</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.951309</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>1.315364</v>
       </c>
     </row>
     <row r="10">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>1.259123</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.92775</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0</v>
+        <v>1.38379</v>
       </c>
     </row>
     <row r="54">
@@ -2898,7 +2898,11 @@
           <t>Equipment 7</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>1.259123</v>
       </c>
@@ -4218,7 +4222,11 @@
           <t>Interest paid $</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -4466,7 +4474,11 @@
           <t>Income taxes paid $</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -4590,7 +4602,11 @@
           <t>Advertising and promotion</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>0.08284900000000001</v>
       </c>
@@ -4648,7 +4664,11 @@
           <t>Consulting 10</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>1.36969</v>
       </c>

--- a/output/pdf_financials_xlsx/TELI.xlsx
+++ b/output/pdf_financials_xlsx/TELI.xlsx
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.356809</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.337008</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.70139</v>
       </c>
     </row>
     <row r="35">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.356809</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.337008</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.70139</v>
       </c>
     </row>
     <row r="37">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.733788</v>
+        <v>0.376979</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.551179</v>
+        <v>0.214171</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.048536</v>
+        <v>0.347146</v>
       </c>
     </row>
     <row r="49">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/TELI.xlsx
+++ b/output/pdf_financials_xlsx/TELI.xlsx
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.035765</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.039602</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.924719</v>
       </c>
     </row>
     <row r="112">
@@ -2587,13 +2587,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.035765</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.039602</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.924719</v>
       </c>
     </row>
     <row r="135">
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.756973</v>
+        <v>-1.792738</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>0.019801</v>
+        <v>-0.019801</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.252063</v>
+        <v>-0.672656</v>
       </c>
     </row>
   </sheetData>
@@ -3955,7 +3955,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>-0.035765</v>
       </c>
